--- a/ListBenefisiersAr.xlsx
+++ b/ListBenefisiersAr.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Houda\Documents\SDL3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41E310B-BC94-4A66-A9AD-E1910F51769E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0AD94D-EAD8-4B57-86B0-7E319432AFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="913" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="913" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="أكبر" sheetId="47" r:id="rId1"/>
     <sheet name="أقل" sheetId="50" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">أقل!$A$6:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">أقل!$A$6:$L$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">أكبر!$A$6:$J$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">أقل!$A$1:$J$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">أكبر!$A$1:$J$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">أقل!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">أكبر!$A$1:$M$51</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
   <si>
     <t>العدد</t>
   </si>
@@ -62,23 +62,29 @@
     <t>ولايـــة توقــرت</t>
   </si>
   <si>
-    <t xml:space="preserve">دائــرة الطيبات </t>
-  </si>
-  <si>
-    <t>القائمـة الاسمية النهائية  للمستفيدين من السكـن العمومــي الايجــاري  (حصـة 2021/87) لبلدية الطيبات  ( فئة اكبر من 35 سنة ) ,  عدد : 52</t>
-  </si>
-  <si>
     <t>الصورة</t>
   </si>
   <si>
-    <t>القائمـة الاسمية النهائية  للمستفيدين من السكـن العمومــي الايجــاري  (حصـة 2021/87) لبلدية الطيبات  ( فئة اقل من 35 سنة ) ,  عدد : 35</t>
+    <t xml:space="preserve">القائمـة الاسمية النهائية  للمستفيدين من السكـن العمومــي الايجــاري  (حصـة ) لبلدية توقرت  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">دائــرة توقرت </t>
+  </si>
+  <si>
+    <t>العنوان</t>
+  </si>
+  <si>
+    <t>تاريخ الإيداع</t>
+  </si>
+  <si>
+    <t>رقم الملف</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,6 +220,12 @@
       <color theme="1"/>
       <name val="Khalid Art bold"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -223,7 +235,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -316,6 +328,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -327,7 +363,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -358,30 +394,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -400,7 +412,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -410,6 +428,9 @@
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -418,7 +439,7 @@
     <cellStyle name="Style 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Style 6" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="32">
     <dxf>
       <font>
         <b/>
@@ -463,6 +484,100 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <charset val="178"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
         <color theme="1"/>
         <name val="Arial"/>
         <family val="2"/>
@@ -756,6 +871,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="double">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="double">
           <color indexed="64"/>
         </left>
@@ -771,30 +893,24 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="double">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="23"/>
-        <color theme="1"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color rgb="FFFF0000"/>
         <name val="Mohammad Head"/>
         <charset val="178"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="double">
           <color indexed="64"/>
@@ -820,12 +936,106 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="23"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <charset val="178"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
         <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="23"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="double">
           <color indexed="64"/>
@@ -854,11 +1064,11 @@
         <vertAlign val="baseline"/>
         <sz val="23"/>
         <color rgb="FFFF0000"/>
-        <name val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="double">
           <color indexed="64"/>
@@ -887,11 +1097,11 @@
         <vertAlign val="baseline"/>
         <sz val="23"/>
         <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="double">
           <color indexed="64"/>
@@ -919,12 +1129,12 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="23"/>
-        <color rgb="FF3333FF"/>
-        <name val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+        <color rgb="FF2525FF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="double">
           <color indexed="64"/>
@@ -952,12 +1162,12 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="23"/>
-        <color rgb="FF008000"/>
-        <name val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+        <color rgb="FF008600"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="double">
           <color indexed="64"/>
@@ -986,11 +1196,12 @@
         <vertAlign val="baseline"/>
         <sz val="23"/>
         <color rgb="FF660066"/>
-        <name val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="double">
           <color indexed="64"/>
@@ -1019,11 +1230,11 @@
         <vertAlign val="baseline"/>
         <sz val="23"/>
         <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="double">
           <color indexed="64"/>
@@ -1052,11 +1263,11 @@
         <vertAlign val="baseline"/>
         <sz val="23"/>
         <color rgb="FFFF0000"/>
-        <name val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="double">
           <color indexed="64"/>
@@ -1085,11 +1296,11 @@
         <vertAlign val="baseline"/>
         <sz val="23"/>
         <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="double">
@@ -1149,38 +1360,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4E969B5A-EB5A-4980-A961-CBF1F21B3A93}" name="Table2" displayName="Table2" ref="A6:J7" insertRow="1" insertRowShift="1" totalsRowShown="0" headerRowBorderDxfId="25" tableBorderDxfId="24" totalsRowBorderDxfId="23">
-  <autoFilter ref="A6:J7" xr:uid="{4E969B5A-EB5A-4980-A961-CBF1F21B3A93}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A4377266-E6FA-480F-AB37-0D3E7EF1BFB3}" name="العدد" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{37E1EA5C-96CC-42F8-8735-ED1F81AD6CE5}" name="اللقــــب" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{20E2CB6F-6FFD-4772-BF1E-2F5EF0A5C608}" name="الاســــم" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{1794612B-27A0-4D2D-8B3A-5336F0E07291}" name="تاريخ الميلاد" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{4EECE675-A17A-465B-91B9-3BEDB4C8299F}" name="بلــدية الميــــلاد" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{6CEE627F-555A-4D3A-AEFA-1366A81F32CB}" name="الحالة العائلية" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{FB56A528-0468-4460-B4E1-838FABD11EC9}" name="اســــــــم الاب" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{C9EC08D0-FD24-4DF0-BC1F-67029300FDF7}" name="لقــــــب الام" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{6999687F-319B-44D5-937F-EDAB8B56AC56}" name="اســــم الام" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{2A78E985-CD7B-46BD-8A45-09DD2988ECE9}" name="الصورة" dataDxfId="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CBEB68F-4E5F-49DF-97B8-8FBBE9C092FE}" name="Table12" displayName="Table12" ref="A6:M7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
+  <autoFilter ref="A6:M7" xr:uid="{9CBEB68F-4E5F-49DF-97B8-8FBBE9C092FE}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{87149A79-0503-4CD2-9209-A403993214BD}" name="العدد" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{E3F5AFD7-AEB0-4478-81F9-2CBC60122C45}" name="اللقــــب" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{F2076430-7DF2-4DDB-9DF3-0658DFB8FB02}" name="الاســــم" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{74FFC9BC-6149-4E30-BB31-9E4DEAE6AB17}" name="تاريخ الميلاد" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{32020190-298E-46C2-9269-AF29721C862F}" name="بلــدية الميــــلاد" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{D04B36C5-3F7C-4E15-9CB6-4052F47BF741}" name="الحالة العائلية" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{6C3D75CB-F159-4F40-A120-484A0A2582DE}" name="اســــــــم الاب" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{275B6AE5-A8CA-4993-A6C9-CED0D43CB222}" name="لقــــــب الام" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{4562D67E-9B0A-4985-B6A1-74AC19546F63}" name="اســــم الام" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{404E6A09-9C96-4768-990E-79E2E9565EFC}" name="العنوان" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{EE38B13D-4BCD-4D60-BF4D-0FC73C75C909}" name="تاريخ الإيداع" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{57E54B80-8104-4DBB-8A5B-129B3F750310}" name="الصورة" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{8288B6CD-DB5E-4401-AD7F-E490AD25C933}" name="رقم الملف" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{89F60721-5F51-427C-BEA5-9C949F3EF5DB}" name="Table1" displayName="Table1" ref="A6:J7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
-  <autoFilter ref="A6:J7" xr:uid="{89F60721-5F51-427C-BEA5-9C949F3EF5DB}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{8A7B8B07-2C0E-43F4-867A-6EC0F836CED3}" name="العدد" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{42EFC0E7-C6DC-41A6-A65D-8586EC95DE99}" name="اللقــــب" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{B0226063-D3EE-435B-A63E-DADB2A66D6AA}" name="الاســــم" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{631F7BEC-FDC4-4225-9DF6-2CF814044773}" name="تاريخ الميلاد" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{8C6F2D4B-BED0-4130-9516-BE1BB7CAFA1D}" name="بلــدية الميــــلاد" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{CFEACD94-0648-4434-AED1-263192E42C2F}" name="الحالة العائلية" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{2C64B0F3-FFD8-4E3F-B988-0A0E2FFAC3B2}" name="اســــــــم الاب" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{CEE003A9-C143-42BF-A77B-C17E8DFBB83A}" name="لقــــــب الام" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{36182AB0-BFB8-4ACF-A498-628E2DC9205A}" name="اســــم الام" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{7CA60E26-7225-464C-B2C3-E83C9094F2AD}" name="الصورة" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{89F60721-5F51-427C-BEA5-9C949F3EF5DB}" name="Table1" displayName="Table1" ref="A6:M7" insertRow="1" totalsRowShown="0" headerRowBorderDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+  <autoFilter ref="A6:M7" xr:uid="{89F60721-5F51-427C-BEA5-9C949F3EF5DB}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{8A7B8B07-2C0E-43F4-867A-6EC0F836CED3}" name="العدد" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{42EFC0E7-C6DC-41A6-A65D-8586EC95DE99}" name="اللقــــب" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{B0226063-D3EE-435B-A63E-DADB2A66D6AA}" name="الاســــم" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{631F7BEC-FDC4-4225-9DF6-2CF814044773}" name="تاريخ الميلاد" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{8C6F2D4B-BED0-4130-9516-BE1BB7CAFA1D}" name="بلــدية الميــــلاد" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{CFEACD94-0648-4434-AED1-263192E42C2F}" name="الحالة العائلية" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{2C64B0F3-FFD8-4E3F-B988-0A0E2FFAC3B2}" name="اســــــــم الاب" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{CEE003A9-C143-42BF-A77B-C17E8DFBB83A}" name="لقــــــب الام" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{36182AB0-BFB8-4ACF-A498-628E2DC9205A}" name="اســــم الام" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{41A880DA-4047-4195-8F9F-BA9052043F76}" name="العنوان" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{78A0F0C2-F173-481D-BB09-04655C2B59BC}" name="تاريخ الإيداع" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{7CA60E26-7225-464C-B2C3-E83C9094F2AD}" name="الصورة" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{17AE5AA6-F1FE-434C-8EF7-A601594BDEEB}" name="رقم الملف" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1474,7 +1691,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -1486,24 +1703,27 @@
     <col min="7" max="7" width="28.85546875" customWidth="1"/>
     <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="54.42578125" customWidth="1"/>
+    <col min="10" max="10" width="44.140625" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
@@ -1516,9 +1736,9 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="3"/>
@@ -1529,31 +1749,31 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="77.25" customHeight="1">
-      <c r="A4" s="27" t="s">
+    <row r="4" spans="1:13" s="1" customFormat="1" ht="77.25" customHeight="1">
+      <c r="A4" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
+    <row r="5" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
     </row>
-    <row r="6" spans="1:10" ht="105.75" customHeight="1" thickBot="1">
+    <row r="6" spans="1:13" ht="105.75" customHeight="1" thickBot="1">
       <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
@@ -1581,21 +1801,33 @@
       <c r="I6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>13</v>
+      <c r="J6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="22" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="200.1" customHeight="1" thickTop="1">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
+    <row r="7" spans="1:13" ht="150" customHeight="1" thickTop="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="13"/>
       <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1614,7 +1846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -1626,24 +1858,27 @@
     <col min="7" max="7" width="28.85546875" customWidth="1"/>
     <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="54.42578125" customWidth="1"/>
+    <col min="10" max="10" width="44.140625" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
@@ -1656,9 +1891,9 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="3"/>
@@ -1669,31 +1904,31 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="77.25" customHeight="1">
-      <c r="A4" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
+    <row r="4" spans="1:13" s="1" customFormat="1" ht="77.25" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
+    <row r="5" spans="1:13" s="1" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
     </row>
-    <row r="6" spans="1:10" ht="105.75" customHeight="1" thickBot="1">
+    <row r="6" spans="1:13" ht="105.75" customHeight="1" thickBot="1">
       <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
@@ -1721,21 +1956,33 @@
       <c r="I6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>13</v>
+      <c r="J6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="22" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="200.1" customHeight="1" thickTop="1">
-      <c r="A7" s="19"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="25"/>
+    <row r="7" spans="1:13" ht="150" customHeight="1" thickTop="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1743,6 +1990,7 @@
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="C5:J5"/>
   </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.19685039370078741" bottom="0" header="0.19685039370078741" footer="0"/>
   <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
